--- a/src/main/resources/datos/Inventario AA V2.xlsx
+++ b/src/main/resources/datos/Inventario AA V2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId3"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="251">
   <si>
     <t xml:space="preserve">(vacío)</t>
   </si>
@@ -754,6 +754,9 @@
   </si>
   <si>
     <t xml:space="preserve">NUM_AVERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCION_DE_REPARADA</t>
   </si>
   <si>
     <t xml:space="preserve">EQUIPO_AVERIADO</t>
@@ -945,7 +948,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1107,13 +1110,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1158,7 +1154,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1372,10 +1368,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1840,9 +1832,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>51480</xdr:colOff>
+      <xdr:colOff>50040</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>84240</xdr:rowOff>
+      <xdr:rowOff>82800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1856,7 +1848,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="679320" y="1638000"/>
-          <a:ext cx="7380000" cy="4084920"/>
+          <a:ext cx="7378560" cy="4083480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6130,47 +6122,47 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="14.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="14.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="59" t="s">
-        <v>236</v>
+      <c r="B1" s="58" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="59"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="59"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="59"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="59"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="59"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6195,8 +6187,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
-        <v>238</v>
+      <c r="A1" s="57" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6247,7 +6239,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6453,7 +6445,7 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6744,7 +6736,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6755,17 +6747,17 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="62" t="s">
-        <v>242</v>
+      <c r="A5" s="61" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6806,13 +6798,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
-        <v>243</v>
+      <c r="A1" s="57" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63" t="s">
-        <v>244</v>
+      <c r="A2" s="62" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6851,36 +6843,36 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="59" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="59" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="64" t="s">
+    <row r="1" s="58" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="63" t="s">
         <v>247</v>
       </c>
-      <c r="D1" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="E1" s="59" t="s">
+      <c r="C1" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="59" t="s">
-        <v>231</v>
-      </c>
-      <c r="H1" s="59" t="s">
+      <c r="G1" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="J1" s="59" t="s">
-        <v>248</v>
+      <c r="J1" s="58" t="s">
+        <v>249</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -6888,7 +6880,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="0"/>
+      <c r="S1" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6913,8 +6905,8 @@
   </cols>
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="65" t="s">
-        <v>249</v>
+      <c r="A1" s="64" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="2" s="26" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12727,38 +12719,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="28.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="27.54"/>
   </cols>
   <sheetData>
     <row r="1" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="52" t="s">
         <v>229</v>
       </c>
       <c r="C1" s="53" t="s">
         <v>230</v>
       </c>
       <c r="D1" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="F1" s="53" t="s">
         <v>131</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>231</v>
       </c>
       <c r="G1" s="53" t="s">
         <v>232</v>
@@ -12767,32 +12760,35 @@
         <v>233</v>
       </c>
       <c r="I1" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="J1" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="XFD1" s="54"/>
-    </row>
-    <row r="2" s="57" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="55"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="XFD2" s="1"/>
+    </row>
+    <row r="2" s="56" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -12825,19 +12821,19 @@
   </cols>
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="58" t="s">
+      <c r="A1" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="C1" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="D1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="D1" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="E1" s="57" t="s">
         <v>142</v>
       </c>
     </row>
@@ -12909,11 +12905,11 @@
   </cols>
   <sheetData>
     <row r="1" s="41" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="59" t="s">
-        <v>236</v>
+      <c r="B1" s="58" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12946,11 +12942,11 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>237</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12989,72 +12985,72 @@
   </cols>
   <sheetData>
     <row r="1" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>237</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="59"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="59"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="59"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="59"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="59"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="59"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="59"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="59"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="59"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="59"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
